--- a/Orlando_Magic_2025-26_stats.xlsx
+++ b/Orlando_Magic_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,35 +484,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Jamal Cain</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Jase Richardson</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Jett Howard</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Goga Bitadze</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Noah Penda</t>
         </is>
@@ -557,18 +562,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>16</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>9</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>8</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -608,21 +616,24 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
         <v>27</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>10</v>
       </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -659,24 +670,27 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>17</v>
-      </c>
-      <c r="M4" t="n">
-        <v>8</v>
       </c>
       <c r="N4" t="n">
         <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -719,18 +733,21 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>22</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>5</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -773,18 +790,21 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>22</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>15</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>10</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -827,18 +847,21 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>21</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>19</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>18</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>6</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -878,21 +901,24 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
         <v>25</v>
       </c>
-      <c r="M8" t="n">
-        <v>2</v>
-      </c>
       <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
         <v>16</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>15</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -932,23 +958,26 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
         <v>18</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>20</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>11</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4</v>
       </c>
       <c r="P9" t="n">
         <v>4</v>
       </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -989,18 +1018,21 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>27</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>11</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>18</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1043,18 +1075,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>20</v>
-      </c>
-      <c r="M11" t="n">
-        <v>12</v>
       </c>
       <c r="N11" t="n">
         <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1094,21 +1129,24 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
         <v>19</v>
       </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
       <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
         <v>19</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>7</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1148,21 +1186,81 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>28</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>8</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>13</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>10</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25</v>
+      </c>
+      <c r="N14" t="n">
+        <v>22</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1177,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,35 +1326,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Jamal Cain</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Jase Richardson</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Jett Howard</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Goga Bitadze</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Noah Penda</t>
         </is>
@@ -1301,18 +1404,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>6</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
         <v>4</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1355,18 +1461,21 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1406,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -1418,9 +1527,12 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1457,24 +1569,27 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1511,24 +1626,27 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1565,24 +1683,27 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1622,21 +1743,24 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
         <v>6</v>
       </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1673,24 +1797,27 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1733,18 +1860,21 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>6</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
       <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1787,18 +1917,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1838,21 +1971,24 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
         <v>6</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
       <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1889,25 +2025,85 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>4</v>
       </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
       <c r="N13" t="n">
         <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1921,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,35 +2168,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Jamal Cain</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Jase Richardson</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Jett Howard</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Goga Bitadze</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Noah Penda</t>
         </is>
@@ -2045,18 +2246,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>4</v>
       </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>8</v>
       </c>
       <c r="P2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2099,18 +2303,21 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>6</v>
       </c>
       <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
         <v>8</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>5</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2153,18 +2360,21 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>7</v>
       </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
       <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
         <v>13</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>9</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2207,18 +2417,21 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
       <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2258,21 +2471,24 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
         <v>6</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2315,18 +2531,21 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
       <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>8</v>
       </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2363,24 +2582,27 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>6</v>
       </c>
-      <c r="M8" t="n">
-        <v>2</v>
-      </c>
       <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
         <v>12</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>6</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2423,18 +2645,21 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>5</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>4</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
       <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2477,18 +2702,21 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>6</v>
       </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
       <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>7</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2531,18 +2759,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>9</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>4</v>
       </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
       <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2582,21 +2813,24 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
         <v>9</v>
       </c>
-      <c r="M12" t="n">
-        <v>3</v>
-      </c>
       <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
         <v>9</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>5</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2639,19 +2873,79 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>9</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>5</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>8</v>
       </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
       <c r="P13" t="n">
         <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2665,7 +2959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2716,35 +3010,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Jamal Cain</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Jase Richardson</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Jett Howard</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Goga Bitadze</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Noah Penda</t>
         </is>
@@ -2789,18 +3088,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2840,21 +3142,24 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2903,12 +3208,15 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2951,18 +3259,21 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3005,18 +3316,21 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3059,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>3</v>
@@ -3068,9 +3382,12 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3110,21 +3427,24 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3164,21 +3484,24 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>4</v>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3221,18 +3544,21 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3275,18 +3601,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3326,21 +3655,24 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3380,21 +3712,81 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3409,7 +3801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3431,7 +3823,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.5</v>
+        <v>22.69230769230769</v>
       </c>
     </row>
     <row r="3">
@@ -3451,47 +3843,47 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.5</v>
+        <v>15.76923076923077</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.66666666666667</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.33333333333333</v>
+        <v>12.23076923076923</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.25</v>
+        <v>11.53846153846154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.66666666666667</v>
+        <v>10.53846153846154</v>
       </c>
     </row>
     <row r="9">
@@ -3501,7 +3893,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.083333333333333</v>
+        <v>6.076923076923077</v>
       </c>
     </row>
     <row r="10">
@@ -3511,27 +3903,27 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.454545454545455</v>
+        <v>2.583333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Noah Penda</t>
+          <t>Jett Howard</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.428571428571428</v>
+        <v>2.555555555555555</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jett Howard</t>
+          <t>Noah Penda</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.125</v>
+        <v>2.428571428571428</v>
       </c>
     </row>
     <row r="13">
@@ -3541,7 +3933,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.666666666666667</v>
+        <v>1.538461538461539</v>
       </c>
     </row>
     <row r="14">
@@ -3561,6 +3953,16 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jamal Cain</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3575,7 +3977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3597,7 +3999,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.666666666666667</v>
+        <v>4.461538461538462</v>
       </c>
     </row>
     <row r="3">
@@ -3607,7 +4009,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.222222222222222</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="4">
@@ -3627,7 +4029,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.75</v>
+        <v>3.846153846153846</v>
       </c>
     </row>
     <row r="6">
@@ -3637,7 +4039,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.333333333333333</v>
+        <v>2.307692307692307</v>
       </c>
     </row>
     <row r="7">
@@ -3647,7 +4049,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.666666666666667</v>
+        <v>1.769230769230769</v>
       </c>
     </row>
     <row r="8">
@@ -3657,7 +4059,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.333333333333333</v>
+        <v>1.384615384615385</v>
       </c>
     </row>
     <row r="9">
@@ -3667,7 +4069,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.25</v>
+        <v>1.153846153846154</v>
       </c>
     </row>
     <row r="10">
@@ -3677,7 +4079,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="11">
@@ -3707,7 +4109,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.625</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="14">
@@ -3717,7 +4119,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -3727,6 +4129,16 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jamal Cain</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3741,7 +4153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3773,7 +4185,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.666666666666667</v>
+        <v>7.461538461538462</v>
       </c>
     </row>
     <row r="4">
@@ -3783,7 +4195,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.416666666666667</v>
+        <v>6.384615384615385</v>
       </c>
     </row>
     <row r="5">
@@ -3793,7 +4205,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.916666666666667</v>
+        <v>5.153846153846154</v>
       </c>
     </row>
     <row r="6">
@@ -3803,7 +4215,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.25</v>
+        <v>4.307692307692307</v>
       </c>
     </row>
     <row r="7">
@@ -3813,27 +4225,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.555555555555555</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.25</v>
+        <v>3.692307692307693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3843,7 +4255,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.363636363636364</v>
+        <v>2.583333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3863,7 +4275,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="13">
@@ -3873,7 +4285,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="14">
@@ -3893,6 +4305,16 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jamal Cain</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3907,7 +4329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3925,21 +4347,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.777777777777778</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -3949,7 +4371,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.583333333333333</v>
+        <v>1.692307692307692</v>
       </c>
     </row>
     <row r="5">
@@ -3959,7 +4381,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.333333333333333</v>
+        <v>1.461538461538461</v>
       </c>
     </row>
     <row r="6">
@@ -3969,7 +4391,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.333333333333333</v>
+        <v>1.230769230769231</v>
       </c>
     </row>
     <row r="7">
@@ -3979,7 +4401,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.166666666666667</v>
+        <v>1.076923076923077</v>
       </c>
     </row>
     <row r="8">
@@ -3999,7 +4421,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.625</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="10">
@@ -4019,7 +4441,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
@@ -4029,7 +4451,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="13">
@@ -4039,7 +4461,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="14">
@@ -4055,10 +4477,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Jamal Cain</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Jase Richardson</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4073,7 +4505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4355,6 +4787,27 @@
         <v>231</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>105</v>
+      </c>
+      <c r="D14" t="n">
+        <v>98</v>
+      </c>
+      <c r="E14" t="n">
+        <v>203</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
